--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -8326,11 +8326,6 @@
       <c r="L114" t="n">
         <v>122</v>
       </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>126891</t>
-        </is>
-      </c>
       <c r="X114" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -25459,7 +25454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27753,17 +27748,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>126891</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Márton</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>KÖVÉR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -27775,17 +27770,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>49666</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Márton</t>
+          <t>Rui</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KÖVÉR</t>
+          <t>LACERDA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -27797,61 +27792,61 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rui</t>
+          <t>Fay</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LACERDA</t>
+          <t>LAMPH</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fay</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LAMPH</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>LEVERETT</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -27863,17 +27858,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LEVERETT</t>
+          <t>LINDBERG</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -27885,61 +27880,61 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Michaela</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LINDBERG</t>
+          <t>LINDBLAD</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michaela</t>
+          <t>Nikica</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LINDBLAD</t>
+          <t>LJUBEK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nikica</t>
+          <t>Edwin</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LJUBEK</t>
+          <t>LUCAS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -27951,61 +27946,61 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35385</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edwin</t>
+          <t>Elisabetta</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LUCAS</t>
+          <t>MAFFIOLI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>50164</t>
+          <t>71674</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Elisabetta</t>
+          <t>Davide</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MAFFIOLI</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Davide</t>
+          <t>Siegl</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -28017,17 +28012,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Siegl</t>
+          <t>Pierrick</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -28039,17 +28034,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pierrick</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>MCCARTHY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -28061,83 +28056,83 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MCCARTHY</t>
+          <t>MCELROY</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Hank</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MCELROY</t>
+          <t>MCGREGOR</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hank</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MCGREGOR</t>
+          <t>MCLAIN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>69449</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Tabea</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MCLAIN</t>
+          <t>MEDERT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -28149,39 +28144,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>49430</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tabea</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MEDERT</t>
+          <t>MERCHÁN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>49430</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MERCHÁN</t>
+          <t>MINDE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -28193,17 +28188,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MINDE</t>
+          <t>MOCKE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -28215,61 +28210,61 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Gwendoline</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MOCKE</t>
+          <t>MOREL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>49436</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gwendoline</t>
+          <t>David Manuel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MOREL</t>
+          <t>MOSQUERA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>49436</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>David Manuel</t>
+          <t>Mohssine</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MOSQUERA</t>
+          <t>MOUTAHIR</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -28281,17 +28276,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mohssine</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MOUTAHIR</t>
+          <t>MULLICAN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -28303,34 +28298,34 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Flóra</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MULLICAN</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Flóra</t>
+          <t>Péter</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -28340,24 +28335,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Péter</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>NATHELL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -28369,61 +28364,61 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Federica</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NATHELL</t>
+          <t>NOLÈ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Federica</t>
+          <t>Dominic</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NOLÈ</t>
+          <t>NOTTEN</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>111726</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Dominic</t>
+          <t>Bálint</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NOTTEN</t>
+          <t>NOÉ</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -28435,17 +28430,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bálint</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NOÉ</t>
+          <t>ODVARKO</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -28457,17 +28452,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Radoslaw</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ODVARKO</t>
+          <t>OLSZEWSKI</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -28479,61 +28474,61 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Radoslaw</t>
+          <t>Amaia</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OLSZEWSKI</t>
+          <t>OSABA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Amaia</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OSABA</t>
+          <t>OVEN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>56984</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Facundo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OVEN</t>
+          <t>PAGIOLA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -28545,17 +28540,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Facundo</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PAGIOLA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28567,17 +28562,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Marcel</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>PAUFLER</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28589,17 +28584,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>63899</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Marcel</t>
+          <t>Hugo Alberto</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PAUFLER</t>
+          <t>PEDRERO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28611,61 +28606,61 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>63899</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Hugo Alberto</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PEDRERO</t>
+          <t>PEDRUELO</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PEDRUELO</t>
+          <t>PENDLE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Artuur</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PENDLE</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -28677,12 +28672,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Artuur</t>
+          <t>Hermien</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -28692,19 +28687,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hermien</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -28714,41 +28709,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Emilie Ahmt</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -28765,39 +28760,39 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Emilie Ahmt</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Ádám</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>PETRÓ</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -28809,17 +28804,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ádám</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PETRÓ</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -28831,61 +28826,61 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>79660</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Hayley</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PLANTE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>79660</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hayley</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PLANTE</t>
+          <t>PLAWSKI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PLAWSKI</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -28897,34 +28892,34 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>71697</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Annemia</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Annemia</t>
+          <t>Casper</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -28934,41 +28929,41 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Casper</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>PÉREZ</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Luis Amado</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -28978,24 +28973,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Luis Amado</t>
+          <t>José</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PÉREZ</t>
+          <t>RAMALHO</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -29007,17 +29002,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>Giorgio</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RAMALHO</t>
+          <t>RICCARDI</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -29029,17 +29024,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Giorgio</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RICCARDI</t>
+          <t>RICE</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -29051,17 +29046,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>48414</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RICE</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -29073,61 +29068,61 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>ROSENKILDE</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>48800</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ROSENKILDE</t>
+          <t>SAELENS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SAELENS</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -29139,17 +29134,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>178014</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Vinicius Zabot</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -29161,17 +29156,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>178014</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Vinicius Zabot</t>
+          <t>Pál</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -29183,17 +29178,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Pál</t>
+          <t>Conrad Robin</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHEIBNER</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -29205,17 +29200,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Conrad Robin</t>
+          <t>Richárd</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SCHEIBNER</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -29227,17 +29222,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Richárd</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -29249,39 +29244,39 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SEGER</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -29293,39 +29288,39 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SEGER</t>
+          <t>SEIDL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SEIDL</t>
+          <t>SHEMETYLO</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -29337,17 +29332,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>Oleksii</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SHEMETYLO</t>
+          <t>SHPAK</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29359,17 +29354,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Oleksii</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SHPAK</t>
+          <t>SIMMONS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29381,61 +29376,61 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Rebeka</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SIMMONS</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Rebeka</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>SINGH</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>100153</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SINGH</t>
+          <t>SIVKOV</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29447,17 +29442,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SIVKOV</t>
+          <t>SLOUF</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29469,61 +29464,61 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Kjinta</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SLOUF</t>
+          <t>SMALLE</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Kjinta</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SMALLE</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>STENLAKE</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -29535,61 +29530,61 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>STENLAKE</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SVENSSON</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Grzegorz</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SVENSSON</t>
+          <t>SZPYNDA</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -29601,17 +29596,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SZPYNDA</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -29623,12 +29618,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>José Manuel</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -29645,17 +29640,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>José Manuel</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -29667,39 +29662,39 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>TAKÁCS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Lisane</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TAKÁCS</t>
+          <t>TERRIE</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -29711,17 +29706,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lisane</t>
+          <t>Amalie</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TERRIE</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -29733,39 +29728,39 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Amalie</t>
+          <t>Leonid</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TILSH</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Leonid</t>
+          <t>Malin</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TILSH</t>
+          <t>TITORIC</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -29777,17 +29772,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Malin</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TITORIC</t>
+          <t>TORSTENSSON</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -29799,17 +29794,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TORSTENSSON</t>
+          <t>TYE</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -29821,17 +29816,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Lars Magne</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TYE</t>
+          <t>ULLVANG</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -29843,17 +29838,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lars Magne</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ULLVANG</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -29865,17 +29860,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VAN DER WALT</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -29887,56 +29882,56 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>VAN DER WALT</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Dávid</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dávid</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -29953,56 +29948,56 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>54279</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miriam</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -30012,112 +30007,112 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>71638</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Miriam</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VERDUYCKT</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Nuria</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>VERDUYCKT</t>
+          <t>VILLACE</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Nuria</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>VILLACE</t>
+          <t>VINCENZI</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Enikö</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>VINCENZI</t>
+          <t>VÁCZAI</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Enikö</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>VÁCZAI</t>
+          <t>WARD</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30129,17 +30124,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>WARD</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -30151,34 +30146,34 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Silvan</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -30195,61 +30190,61 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Silvan</t>
+          <t>Penelope</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YOUNG</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Penelope</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>YOUNG</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZUCHORA</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -30261,17 +30256,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ZUCHORA</t>
+          <t>ÁVILA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -30283,42 +30278,20 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ÁVILA</t>
+          <t>ÚRSULA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>49516</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>ÚRSULA</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -2493,11 +2493,6 @@
           <t>+10:23,240</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>178014</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11886,11 +11881,6 @@
       <c r="Q165" t="inlineStr">
         <is>
           <t>+9:51,760</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>178014</t>
         </is>
       </c>
     </row>
@@ -25454,7 +25444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29134,17 +29124,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>178014</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vinicius Zabot</t>
+          <t>Pál</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -29156,17 +29146,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Pál</t>
+          <t>Conrad Robin</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHEIBNER</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -29178,17 +29168,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Conrad Robin</t>
+          <t>Richárd</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SCHEIBNER</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -29200,17 +29190,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Richárd</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -29222,39 +29212,39 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SEGER</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -29266,39 +29256,39 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SEGER</t>
+          <t>SEIDL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SEIDL</t>
+          <t>SHEMETYLO</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -29310,17 +29300,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>Oleksii</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SHEMETYLO</t>
+          <t>SHPAK</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -29332,17 +29322,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Oleksii</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SHPAK</t>
+          <t>SIMMONS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29354,61 +29344,61 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Rebeka</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SIMMONS</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Rebeka</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>SINGH</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>100153</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SINGH</t>
+          <t>SIVKOV</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29420,17 +29410,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SIVKOV</t>
+          <t>SLOUF</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29442,61 +29432,61 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Kjinta</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SLOUF</t>
+          <t>SMALLE</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Kjinta</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SMALLE</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>STENLAKE</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -29508,61 +29498,61 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>STENLAKE</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SVENSSON</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Grzegorz</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SVENSSON</t>
+          <t>SZPYNDA</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -29574,17 +29564,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SZPYNDA</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -29596,12 +29586,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>José Manuel</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -29618,17 +29608,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>José Manuel</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -29640,39 +29630,39 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>TAKÁCS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Lisane</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TAKÁCS</t>
+          <t>TERRIE</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -29684,17 +29674,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lisane</t>
+          <t>Amalie</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TERRIE</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -29706,39 +29696,39 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Amalie</t>
+          <t>Leonid</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TILSH</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Leonid</t>
+          <t>Malin</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TILSH</t>
+          <t>TITORIC</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -29750,17 +29740,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Malin</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TITORIC</t>
+          <t>TORSTENSSON</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -29772,17 +29762,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TORSTENSSON</t>
+          <t>TYE</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -29794,17 +29784,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Lars Magne</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TYE</t>
+          <t>ULLVANG</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -29816,17 +29806,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lars Magne</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ULLVANG</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -29838,17 +29828,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VAN DER WALT</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -29860,56 +29850,56 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>VAN DER WALT</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Dávid</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Dávid</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -29926,56 +29916,56 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>54279</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miriam</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -29985,112 +29975,112 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>71638</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Miriam</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VERDUYCKT</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Nuria</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VERDUYCKT</t>
+          <t>VILLACE</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Nuria</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>VILLACE</t>
+          <t>VINCENZI</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Enikö</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>VINCENZI</t>
+          <t>VÁCZAI</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Enikö</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>VÁCZAI</t>
+          <t>WARD</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -30102,17 +30092,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>WARD</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30124,34 +30114,34 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Silvan</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -30168,61 +30158,61 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Silvan</t>
+          <t>Penelope</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YOUNG</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Penelope</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>YOUNG</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZUCHORA</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30234,17 +30224,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ZUCHORA</t>
+          <t>ÁVILA</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -30256,42 +30246,20 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ÁVILA</t>
+          <t>ÚRSULA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>49516</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>ÚRSULA</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -13145,11 +13145,6 @@
           <t>+6:03,000</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>85415</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -25444,7 +25439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27100,17 +27095,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Francesca</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GARCÍA</t>
+          <t>GENZO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -27122,39 +27117,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>64651</t>
+          <t>49642</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Francesca</t>
+          <t>Zsolt</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GENZO</t>
+          <t>GILÁNYI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>49642</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zsolt</t>
+          <t>Wiktor</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GILÁNYI</t>
+          <t>GLAZUNOW</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -27166,17 +27161,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wiktor</t>
+          <t>Patryk</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GLAZUNOW</t>
+          <t>GLUZA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -27188,17 +27183,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>42851</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Patryk</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GLUZA</t>
+          <t>GRAVERSEN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -27210,17 +27205,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GRAVERSEN</t>
+          <t>GRAÑA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -27232,17 +27227,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Attila</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GRAÑA</t>
+          <t>GYÖRE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -27254,39 +27249,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>52222</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Attila</t>
+          <t>Réka</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GYÖRE</t>
+          <t>HAGYMÁSI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>52222</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Réka</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HAGYMÁSI</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -27298,39 +27293,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Gordon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HARBRECHT</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>48492</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gordon</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HARBRECHT</t>
+          <t>HICKS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -27342,17 +27337,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>48492</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Lars</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HICKS</t>
+          <t>HJEMDAL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -27364,39 +27359,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lars</t>
+          <t>Noémi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HJEMDAL</t>
+          <t>HORVÁTH</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Noémi</t>
+          <t>Lenka</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HORVÁTH</t>
+          <t>HROCHOVA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -27408,61 +27403,61 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lenka</t>
+          <t>Dmytro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HROCHOVA</t>
+          <t>IANCHUK</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dmytro</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IANCHUK</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>68309</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>ILLIDGE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -27474,39 +27469,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>45123</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Richárd</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ILLIDGE</t>
+          <t>JANZA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>45123</t>
+          <t>49732</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Richárd</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JANZA</t>
+          <t>JEZEK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -27518,61 +27513,61 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>54948</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Johanna</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JEZEK</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Johanna</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>JOHNSON</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JOHNSON</t>
+          <t>KAMINSKI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -27584,17 +27579,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>66568</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Joosep</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KAMINSKI</t>
+          <t>KARLSON</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -27606,39 +27601,39 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>66568</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Joosep</t>
+          <t>Vanda</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KARLSON</t>
+          <t>KISZLI</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Vanda</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KISZLI</t>
+          <t>KLEIN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -27650,83 +27645,83 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Tamás</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KLEIN</t>
+          <t>KORONDY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tamás</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KORONDY</t>
+          <t>KOZISKOVA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KOZISKOVA</t>
+          <t>KRAJEWSKI</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>49666</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Márton</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KRAJEWSKI</t>
+          <t>KÖVÉR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -27738,17 +27733,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>49666</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Márton</t>
+          <t>Rui</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KÖVÉR</t>
+          <t>LACERDA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -27760,61 +27755,61 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rui</t>
+          <t>Fay</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LACERDA</t>
+          <t>LAMPH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fay</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LAMPH</t>
+          <t>LASCANO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LASCANO</t>
+          <t>LEVERETT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -27826,17 +27821,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LEVERETT</t>
+          <t>LINDBERG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -27848,61 +27843,61 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Michaela</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LINDBERG</t>
+          <t>LINDBLAD</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Michaela</t>
+          <t>Nikica</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LINDBLAD</t>
+          <t>LJUBEK</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nikica</t>
+          <t>Edwin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LJUBEK</t>
+          <t>LUCAS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -27914,61 +27909,61 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35385</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edwin</t>
+          <t>Elisabetta</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LUCAS</t>
+          <t>MAFFIOLI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>50164</t>
+          <t>71674</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Elisabetta</t>
+          <t>Davide</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MAFFIOLI</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>71674</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Davide</t>
+          <t>Siegl</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MARIN</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -27980,17 +27975,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Siegl</t>
+          <t>Pierrick</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -28002,17 +27997,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pierrick</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>MCCARTHY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -28024,83 +28019,83 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MCCARTHY</t>
+          <t>MCELROY</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Hank</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MCELROY</t>
+          <t>MCGREGOR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hank</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MCGREGOR</t>
+          <t>MCLAIN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>69449</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Tabea</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MCLAIN</t>
+          <t>MEDERT</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -28112,39 +28107,39 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>49430</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tabea</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MEDERT</t>
+          <t>MERCHÁN</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>49430</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MERCHÁN</t>
+          <t>MINDE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -28156,17 +28151,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MINDE</t>
+          <t>MOCKE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -28178,61 +28173,61 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Gwendoline</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MOCKE</t>
+          <t>MOREL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>49436</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gwendoline</t>
+          <t>David Manuel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MOREL</t>
+          <t>MOSQUERA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>49436</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>David Manuel</t>
+          <t>Mohssine</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MOSQUERA</t>
+          <t>MOUTAHIR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -28244,17 +28239,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mohssine</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MOUTAHIR</t>
+          <t>MULLICAN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -28266,34 +28261,34 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>52281</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Flóra</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MULLICAN</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Flóra</t>
+          <t>Péter</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -28303,24 +28298,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Péter</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>NATHELL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -28332,61 +28327,61 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Federica</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NATHELL</t>
+          <t>NOLÈ</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>111726</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Federica</t>
+          <t>Dominic</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NOLÈ</t>
+          <t>NOTTEN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>111726</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dominic</t>
+          <t>Bálint</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NOTTEN</t>
+          <t>NOÉ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -28398,17 +28393,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bálint</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NOÉ</t>
+          <t>ODVARKO</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -28420,17 +28415,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Radoslaw</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ODVARKO</t>
+          <t>OLSZEWSKI</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -28442,61 +28437,61 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Radoslaw</t>
+          <t>Amaia</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OLSZEWSKI</t>
+          <t>OSABA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Amaia</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OSABA</t>
+          <t>OVEN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>56984</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Facundo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OVEN</t>
+          <t>PAGIOLA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -28508,17 +28503,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Facundo</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PAGIOLA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -28530,17 +28525,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Marcel</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>PAUFLER</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28552,17 +28547,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>63899</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Marcel</t>
+          <t>Hugo Alberto</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PAUFLER</t>
+          <t>PEDRERO</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28574,61 +28569,61 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>63899</t>
+          <t>46832</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hugo Alberto</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PEDRERO</t>
+          <t>PEDRUELO</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>46832</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PEDRUELO</t>
+          <t>PENDLE</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Artuur</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PENDLE</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28640,12 +28635,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Artuur</t>
+          <t>Hermien</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -28655,19 +28650,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hermien</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -28677,41 +28672,41 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Emilie Ahmt</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -28728,39 +28723,39 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Emilie Ahmt</t>
+          <t>Vladimir</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vladimir</t>
+          <t>Ádám</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>PETRÓ</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -28772,17 +28767,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ádám</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PETRÓ</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -28794,61 +28789,61 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>79660</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Hayley</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PLANTE</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>79660</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hayley</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PLANTE</t>
+          <t>PLAWSKI</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PLAWSKI</t>
+          <t>PLAZA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -28860,34 +28855,34 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>71697</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Annemia</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PLAZA</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Annemia</t>
+          <t>Casper</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -28897,41 +28892,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Casper</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>PÉREZ</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Luis Amado</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -28941,24 +28936,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Luis Amado</t>
+          <t>José</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PÉREZ</t>
+          <t>RAMALHO</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -28970,17 +28965,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>José</t>
+          <t>Giorgio</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RAMALHO</t>
+          <t>RICCARDI</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -28992,17 +28987,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Giorgio</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RICCARDI</t>
+          <t>RICE</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -29014,17 +29009,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>48414</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RICE</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -29036,61 +29031,61 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>ROSENKILDE</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>48800</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ROSENKILDE</t>
+          <t>SAELENS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SAELENS</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -29102,17 +29097,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Pál</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -29124,17 +29119,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Pál</t>
+          <t>Conrad Robin</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHEIBNER</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -29146,17 +29141,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Conrad Robin</t>
+          <t>Richárd</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SCHEIBNER</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -29168,17 +29163,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Richárd</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -29190,39 +29185,39 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SEGER</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -29234,39 +29229,39 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEGER</t>
+          <t>SEIDL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SEIDL</t>
+          <t>SHEMETYLO</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -29278,17 +29273,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>Oleksii</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SHEMETYLO</t>
+          <t>SHPAK</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -29300,17 +29295,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Oleksii</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SHPAK</t>
+          <t>SIMMONS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -29322,61 +29317,61 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Rebeka</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIMMONS</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Rebeka</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>SINGH</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>100153</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SINGH</t>
+          <t>SIVKOV</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29388,17 +29383,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SIVKOV</t>
+          <t>SLOUF</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29410,61 +29405,61 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Kjinta</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SLOUF</t>
+          <t>SMALLE</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kjinta</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SMALLE</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>STENLAKE</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -29476,61 +29471,61 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>STENLAKE</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SVENSSON</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Grzegorz</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SVENSSON</t>
+          <t>SZPYNDA</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -29542,17 +29537,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SZPYNDA</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -29564,12 +29559,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>José Manuel</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -29586,17 +29581,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>José Manuel</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -29608,39 +29603,39 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>TAKÁCS</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Lisane</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TAKÁCS</t>
+          <t>TERRIE</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -29652,17 +29647,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lisane</t>
+          <t>Amalie</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TERRIE</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -29674,39 +29669,39 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Amalie</t>
+          <t>Leonid</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TILSH</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Leonid</t>
+          <t>Malin</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TILSH</t>
+          <t>TITORIC</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -29718,17 +29713,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Malin</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TITORIC</t>
+          <t>TORSTENSSON</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -29740,17 +29735,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TORSTENSSON</t>
+          <t>TYE</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -29762,17 +29757,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Lars Magne</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TYE</t>
+          <t>ULLVANG</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -29784,17 +29779,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lars Magne</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ULLVANG</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -29806,17 +29801,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VAN DER WALT</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -29828,56 +29823,56 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>VAN DER WALT</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Dávid</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Dávid</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -29894,56 +29889,56 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>54279</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miriam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -29953,112 +29948,112 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>71638</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Miriam</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VERDUYCKT</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Nuria</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VERDUYCKT</t>
+          <t>VILLACE</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nuria</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VILLACE</t>
+          <t>VINCENZI</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Enikö</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>VINCENZI</t>
+          <t>VÁCZAI</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Enikö</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>VÁCZAI</t>
+          <t>WARD</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -30070,17 +30065,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>WARD</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -30092,34 +30087,34 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Silvan</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -30136,61 +30131,61 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Silvan</t>
+          <t>Penelope</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YOUNG</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Penelope</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>YOUNG</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZUCHORA</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -30202,17 +30197,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ZUCHORA</t>
+          <t>ÁVILA</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30224,42 +30219,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ÁVILA</t>
+          <t>ÚRSULA</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>49516</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>ÚRSULA</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -17528,6 +17528,11 @@
       <c r="L247" t="n">
         <v>343</v>
       </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
       <c r="X247" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -22163,6 +22168,11 @@
           <t>+1:43,150</t>
         </is>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -23902,6 +23912,11 @@
       <c r="Q339" t="inlineStr">
         <is>
           <t>+4:21,850</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>58936</t>
         </is>
       </c>
     </row>
@@ -25439,7 +25454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D218"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30238,6 +30253,50 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>58936</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nestor</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>PINTA</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -748,6 +748,11 @@
           <t>+0:08,680</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>49665</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9381,6 +9386,11 @@
           <t>+2:38,940</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10669,6 +10679,11 @@
           <t>+2:25,160</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>49665</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13073,6 +13088,11 @@
           <t>+5:05,050</t>
         </is>
       </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>72593</t>
+        </is>
+      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>57972</t>
@@ -13566,6 +13586,11 @@
           <t>42842</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="X189" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -18133,6 +18158,11 @@
           <t>+0:55,290</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -23919,6 +23949,11 @@
           <t>58936</t>
         </is>
       </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>58937</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -24279,6 +24314,11 @@
           <t>35992</t>
         </is>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>48191</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -25146,6 +25186,11 @@
       </c>
       <c r="L357" t="n">
         <v>464</v>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>49621</t>
+        </is>
       </c>
       <c r="X357" t="inlineStr">
         <is>
@@ -25454,7 +25499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30297,6 +30342,182 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Emma Aastrand</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>JORGENSEN</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>48191</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Mathias</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>HAMAR</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>49621</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Nicolai</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>BLACH</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>49665</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Balazs</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HAVAS</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>58937</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Leonardo Martin</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>MOZZICAFREDO</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>72593</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Tania</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -9602,11 +9602,6 @@
           <t>+3:46,710</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>48800</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13165,6 +13160,11 @@
           <t>+6:03,000</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>85415</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -23870,11 +23870,6 @@
       <c r="R338" t="inlineStr">
         <is>
           <t>48584</t>
-        </is>
-      </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>48800</t>
         </is>
       </c>
     </row>
@@ -29113,17 +29108,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SAELENS</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -29135,17 +29130,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Pál</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -29157,17 +29152,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Pál</t>
+          <t>Conrad Robin</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHEIBNER</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -29179,17 +29174,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>49656</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Conrad Robin</t>
+          <t>Richárd</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SCHEIBNER</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -29201,17 +29196,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Richárd</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -29223,39 +29218,39 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SEGER</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -29267,39 +29262,39 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SEGER</t>
+          <t>SEIDL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEIDL</t>
+          <t>SHEMETYLO</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -29311,17 +29306,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>Oleksii</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>SHEMETYLO</t>
+          <t>SHPAK</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -29333,17 +29328,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>88454</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Oleksii</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SHPAK</t>
+          <t>SIMMONS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -29355,61 +29350,61 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>88454</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Rebeka</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SIMMONS</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>100153</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rebeka</t>
+          <t>Ajit</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>SINGH</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>100153</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ajit</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SINGH</t>
+          <t>SIVKOV</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29421,17 +29416,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>42376</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SIVKOV</t>
+          <t>SLOUF</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29443,61 +29438,61 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Kjinta</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SLOUF</t>
+          <t>SMALLE</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Kjinta</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SMALLE</t>
+          <t>SOLARES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>49447</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>SOLARES</t>
+          <t>STENLAKE</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29509,61 +29504,61 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>STENLAKE</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SVENSSON</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Grzegorz</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SVENSSON</t>
+          <t>SZPYNDA</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -29575,17 +29570,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>57974</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SZPYNDA</t>
+          <t>SÁNCHEZ</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -29597,12 +29592,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>José Manuel</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -29619,17 +29614,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>José Manuel</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SÁNCHEZ</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -29641,39 +29636,39 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>TAKÁCS</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Lisane</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TAKÁCS</t>
+          <t>TERRIE</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -29685,17 +29680,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lisane</t>
+          <t>Amalie</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TERRIE</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -29707,39 +29702,39 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Amalie</t>
+          <t>Leonid</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TILSH</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>36184</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Leonid</t>
+          <t>Malin</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TILSH</t>
+          <t>TITORIC</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -29751,17 +29746,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Malin</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TITORIC</t>
+          <t>TORSTENSSON</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -29773,17 +29768,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TORSTENSSON</t>
+          <t>TYE</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -29795,17 +29790,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Lars Magne</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TYE</t>
+          <t>ULLVANG</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -29817,17 +29812,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lars Magne</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>ULLVANG</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -29839,17 +29834,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VAN DER WALT</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -29861,56 +29856,56 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>56464</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>VAN DER WALT</t>
+          <t>VARELA</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Dávid</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>VARELA</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dávid</t>
+          <t>Patrik</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -29927,56 +29922,56 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>54279</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Patrik</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Miriam</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -29986,112 +29981,112 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>71638</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Miriam</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VERDUYCKT</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>71638</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Nuria</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>VERDUYCKT</t>
+          <t>VILLACE</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Nuria</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VILLACE</t>
+          <t>VINCENZI</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Enikö</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VINCENZI</t>
+          <t>VÁCZAI</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Enikö</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>VÁCZAI</t>
+          <t>WARD</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -30103,17 +30098,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>WARD</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -30125,34 +30120,34 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Silvan</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -30169,61 +30164,61 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Silvan</t>
+          <t>Penelope</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YOUNG</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Penelope</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>YOUNG</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZUCHORA</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30235,17 +30230,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ZUCHORA</t>
+          <t>ÁVILA</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -30257,17 +30252,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ÁVILA</t>
+          <t>ÚRSULA</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30279,17 +30274,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Nuno</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>ÚRSULA</t>
+          <t>BARROS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -30301,17 +30296,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>58936</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nuno</t>
+          <t>Nestor</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BARROS</t>
+          <t>PINTA</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -30323,61 +30318,61 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nestor</t>
+          <t>Emma Aastrand</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>PINTA</t>
+          <t>JORGENSEN</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>42844</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Emma Aastrand</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>JORGENSEN</t>
+          <t>HAMAR</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>48191</t>
+          <t>49621</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Nicolai</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>HAMAR</t>
+          <t>BLACH</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -30389,17 +30384,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>49621</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nicolai</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BLACH</t>
+          <t>BOROS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -30411,17 +30406,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>49663</t>
+          <t>49665</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Balazs</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>BOROS</t>
+          <t>HAVAS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -30433,17 +30428,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Balazs</t>
+          <t>Joep</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HAVAS</t>
+          <t>BAKEL VAN</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30455,17 +30450,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Joep</t>
+          <t>Leonardo Martin</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BAKEL VAN</t>
+          <t>MOZZICAFREDO</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30477,39 +30472,39 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Leonardo Martin</t>
+          <t>Tania</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MOZZICAFREDO</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Tania</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>DOMINGUEZ GARCIA</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -13160,11 +13160,6 @@
           <t>+6:03,000</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>85415</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -25494,7 +25489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30491,28 +30486,6 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>85415</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>DOMINGUEZ GARCIA</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
+++ b/events/Rome_2012_MAR/Rome_2012_MAR_Results.xlsx
@@ -11553,6 +11553,11 @@
           <t>+6:53,110</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>74023</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -25489,7 +25494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30486,6 +30491,28 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>74023</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>COUCQUYT</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
